--- a/downloads/loesungen/12_FestivalCrew_3NF_Loesung.xlsx
+++ b/downloads/loesungen/12_FestivalCrew_3NF_Loesung.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW" sheetId="1" r:id="R1c467c3f8a9d40f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEAM" sheetId="2" r:id="R6b27ae2fcc31417f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORKSHOP" sheetId="3" r:id="R84f8d3545211494d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAUM" sheetId="4" r:id="Ra211d4618d0b4557"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW_WORKSHOP" sheetId="5" r:id="R7ec5137759774364"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW" sheetId="1" r:id="R18a40a93082a4187"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEAM" sheetId="2" r:id="Rcc57e0373f5842f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WORKSHOP" sheetId="3" r:id="R6165bfee56f14f4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAUM" sheetId="4" r:id="R95017ab74188440c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CREW_WORKSHOP" sheetId="5" r:id="R3d7d5a724ec64fa8"/>
   </x:sheets>
 </x:workbook>
 </file>
